--- a/hall/resources/sample/SeasondropDetailed.xlsx
+++ b/hall/resources/sample/SeasondropDetailed.xlsx
@@ -50,13 +50,13 @@
     <t>白色宝石</t>
   </si>
   <si>
-    <t>100_10101_1|100_10201_1</t>
+    <t>100_100101_1|100_100201_1</t>
   </si>
   <si>
     <t>绿色宝石</t>
   </si>
   <si>
-    <t>100_10102_1|100_10202_1</t>
+    <t>100_100102_1|100_100202_1</t>
   </si>
 </sst>
 </file>

--- a/hall/resources/sample/SeasondropDetailed.xlsx
+++ b/hall/resources/sample/SeasondropDetailed.xlsx
@@ -1,13 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SeasondropDetailed" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,13 +56,13 @@
     <t>白色宝石</t>
   </si>
   <si>
-    <t>100_100101_1|100_100201_1</t>
+    <t>1000_100101_1|1000_100106_1|1000_100201_1|1000_100206_1|1000_100301_1|1000_100306_1|1000_100311_1</t>
   </si>
   <si>
     <t>绿色宝石</t>
   </si>
   <si>
-    <t>100_100102_1|100_100202_1</t>
+    <t>500_100102_1|500_100107_1|500_100202_1|500_100207_1|500_100302_1|500_100307_1|500_100312_1</t>
   </si>
 </sst>
 </file>
@@ -1274,4 +1280,166 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="G6:K24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData>
+    <row r="6" spans="7:11">
+      <c r="K6" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,K7:K13)</f>
+        <v>1000_100101_1|1000_100106_1|1000_100201_1|1000_100206_1|1000_100301_1|1000_100306_1|1000_100311_1</v>
+      </c>
+    </row>
+    <row r="7" spans="7:11">
+      <c r="G7">
+        <v>1000</v>
+      </c>
+      <c r="H7">
+        <v>100101</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="K7" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,$G$7,H7,$I$7)</f>
+        <v>1000_100101_1</v>
+      </c>
+    </row>
+    <row r="8" spans="7:11">
+      <c r="H8">
+        <v>100106</v>
+      </c>
+      <c r="K8" t="str">
+        <f t="shared" ref="K8:K13" si="0">_xlfn.TEXTJOIN("_",TRUE,$G$7,H8,$I$7)</f>
+        <v>1000_100106_1</v>
+      </c>
+    </row>
+    <row r="9" spans="7:11">
+      <c r="H9">
+        <v>100201</v>
+      </c>
+      <c r="K9" t="str">
+        <f t="shared" si="0"/>
+        <v>1000_100201_1</v>
+      </c>
+    </row>
+    <row r="10" spans="7:11">
+      <c r="H10">
+        <v>100206</v>
+      </c>
+      <c r="K10" t="str">
+        <f t="shared" si="0"/>
+        <v>1000_100206_1</v>
+      </c>
+    </row>
+    <row r="11" spans="7:11">
+      <c r="H11">
+        <v>100301</v>
+      </c>
+      <c r="K11" t="str">
+        <f t="shared" si="0"/>
+        <v>1000_100301_1</v>
+      </c>
+    </row>
+    <row r="12" spans="7:11">
+      <c r="H12">
+        <v>100306</v>
+      </c>
+      <c r="K12" t="str">
+        <f t="shared" si="0"/>
+        <v>1000_100306_1</v>
+      </c>
+    </row>
+    <row r="13" spans="7:11">
+      <c r="H13">
+        <v>100311</v>
+      </c>
+      <c r="K13" t="str">
+        <f t="shared" si="0"/>
+        <v>1000_100311_1</v>
+      </c>
+    </row>
+    <row r="17" spans="7:11">
+      <c r="K17" t="str">
+        <f>_xlfn.TEXTJOIN("|",TRUE,K18:K24)</f>
+        <v>500_100102_1|500_100107_1|500_100202_1|500_100207_1|500_100302_1|500_100307_1|500_100312_1</v>
+      </c>
+    </row>
+    <row r="18" spans="7:11">
+      <c r="G18">
+        <v>500</v>
+      </c>
+      <c r="H18">
+        <v>100102</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="K18" t="str">
+        <f>_xlfn.TEXTJOIN("_",TRUE,$G$18,H18,$I$18)</f>
+        <v>500_100102_1</v>
+      </c>
+    </row>
+    <row r="19" spans="7:11">
+      <c r="H19">
+        <v>100107</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" ref="K19:K24" si="1">_xlfn.TEXTJOIN("_",TRUE,$G$18,H19,$I$18)</f>
+        <v>500_100107_1</v>
+      </c>
+    </row>
+    <row r="20" spans="7:11">
+      <c r="H20">
+        <v>100202</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="1"/>
+        <v>500_100202_1</v>
+      </c>
+    </row>
+    <row r="21" spans="7:11">
+      <c r="H21">
+        <v>100207</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="1"/>
+        <v>500_100207_1</v>
+      </c>
+    </row>
+    <row r="22" spans="7:11">
+      <c r="H22">
+        <v>100302</v>
+      </c>
+      <c r="K22" t="str">
+        <f t="shared" si="1"/>
+        <v>500_100302_1</v>
+      </c>
+    </row>
+    <row r="23" spans="7:11">
+      <c r="H23">
+        <v>100307</v>
+      </c>
+      <c r="K23" t="str">
+        <f t="shared" si="1"/>
+        <v>500_100307_1</v>
+      </c>
+    </row>
+    <row r="24" spans="7:11">
+      <c r="H24">
+        <v>100312</v>
+      </c>
+      <c r="K24" t="str">
+        <f t="shared" si="1"/>
+        <v>500_100312_1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>